--- a/deliverables/business/financial-model.xlsx
+++ b/deliverables/business/financial-model.xlsx
@@ -681,14 +681,14 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Financial Model — 36-month SaPS projection (v2.0, honest base case)</t>
+          <t>Financial Model — 36-month SaPS projection (v2.1, Zimbabwe bootstrap)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>v2.0  ·  Tatenda Nyemudzo  ·  June 2026  ·  supersedes the May-2026 model</t>
+          <t>v2.1  ·  Tatenda Nyemudzo  ·  June 2026  ·  bootstrap frame (no capital, no salary)</t>
         </is>
       </c>
     </row>
@@ -729,14 +729,14 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>4. Costs         — Founder-lean headcount + infrastructure.</t>
+          <t>4. Costs         — Lean operating costs only (NO founder salary — bootstrap).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>5. P&amp;L summary   — Month-by-month revenue, costs, net, cumulative + notes.</t>
+          <t>5. P&amp;L summary   — Month-by-month revenue, costs, surplus, cumulative + notes.</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>WHY v2.0 — WHAT CHANGED FROM THE MAY MODEL</t>
+          <t>THE FRAME — A ZIMBABWE BOOTSTRAP</t>
         </is>
       </c>
     </row>
@@ -759,166 +759,166 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>·  The May model assumed 10 houses in 33 months and 70% digital adoption. For a startup</t>
+          <t>·  This is NOT modelled like a first-world startup. There is no VC to raise from, no</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   breaking a legacy, manual, cash-based market in Zimbabwe, both were over-optimistic.</t>
+          <t xml:space="preserve">   founder salary financed by capital, and no 'burn toward a break-even month'.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>·  Customer ramp:    10 houses  -&gt;  3 houses (1 -&gt; 2 -&gt; 3).</t>
+          <t>·  The founder is an owner-operator. Their income IS the operating surplus below.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>·  Adoption ceiling: 70%        -&gt;  15% (slow trust-building vs $1,000 cash deposits).</t>
+          <t>·  No external capital is assumed or required. Growth is funded out of surplus.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>·  Pricing:          Tier A $10-12k/$2-2.5k  -&gt;  $8k/$1.5k (realistic USD WTP).</t>
+          <t>·  vs the May model: 10 houses -&gt; 3; 70% adoption -&gt; 15%; Tier A $10-12k/$2-2.5k -&gt; $8k/$1.5k.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>·  Costs:            funded org chart        -&gt;  founder-lean.</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="4" t="inlineStr"/>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="4" t="inlineStr"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>HONEST HEADLINE OUTPUTS (Zimbabwe bootstrap)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>HONEST HEADLINE OUTPUTS (leanest base case)</t>
-        </is>
-      </c>
+      <c r="A25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="4" t="inlineStr"/>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>·  Year 1:  revenue ~$12,000   cost ~$6,000    founder income ~+$6,000   (1 house)</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>·  Year 1 revenue:        ~$12,000     net  ~-$19,000   (1 house)</t>
+          <t>·  Year 2:  revenue ~$28,000   cost ~$10,000   founder income ~+$18,000  (2 houses)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>·  Year 2 revenue:        ~$28,000     net  ~-$13,000   (2 houses)</t>
+          <t>·  Year 3:  revenue ~$49,000   cost ~$17,000   founder income ~+$32,000  (3 houses)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>·  Year 3 revenue:        ~$49,000     net   ~-$7,000   (3 houses)</t>
+          <t>·  3-year:  revenue ~$89,000   founder earns ~+$56,000 over 3 years.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>·  3-year revenue:        ~$89,000     3-yr net  ~-$39,000</t>
+          <t>·  Cash-positive from the first live house. Max ever out-of-pocket ~$2,250 (self-financed).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>·  Standalone break-even: BEYOND month 36 — investment-stage throughout.</t>
+          <t>·  External capital required: $0.   GMV onto Paynow rails: ~$43k -&gt; ~$223k -&gt; ~$545k.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>·  GMV onto Paynow rails: ~$43k -&gt; ~$223k -&gt; ~$545k  (grows fastest).</t>
-        </is>
-      </c>
+      <c r="A32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="4" t="inlineStr"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>THE KEY INSIGHT</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>THE KEY INSIGHT</t>
-        </is>
-      </c>
+      <c r="A34" s="4" t="inlineStr"/>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="4" t="inlineStr"/>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>·  Constraint is SCALE + OPERATOR CAPACITY, not adoption. Per-house economics work</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>·  Constraint is SCALE + FIXED COST, not adoption. Per-house economics work</t>
+          <t xml:space="preserve">   (~$15-30k/yr surplus per mature house). Doubling adoption (15% -&gt; 30%) adds only ~$200/mo.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (~$15-21k/yr contribution per mature house); the model needs ~5-6 houses to cover the</t>
+          <t>·  More houses = more income, capped by what one owner + cheap part-time help can run well.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   founder + support base. Doubling adoption (15% -&gt; 30%) recovers only ~$200/mo.</t>
-        </is>
-      </c>
+      <c r="A38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="4" t="inlineStr"/>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>HOW IT SCALES (no capital, no raise)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>PATH TO VIABILITY (upside, NOT base case)</t>
-        </is>
-      </c>
+      <c r="A40" s="4" t="inlineStr"/>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="4" t="inlineStr"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>·  Each new house is funded from the surplus of the last. The founder reinvests part of</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>·  6 houses by month 44 + 20% adoption + transport margin  -&gt;  cumulative break-even</t>
+          <t xml:space="preserve">   the surplus into part-time help to take on the next house. Slow, self-funded, durable.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ~month 36, and ~+$103,000 cumulative by month 60. See 5. P&amp;L summary notes.</t>
-        </is>
-      </c>
+      <c r="A43" s="4" t="inlineStr"/>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="4" t="inlineStr"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>·  Zim risks: USD scarcity / collection friction, currency volatility, no capital cushion.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -1207,48 +1207,48 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>COSTS — founder-lean (USD/month)</t>
+          <t>COSTS — Zimbabwe bootstrap (USD/month, no founder salary)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Founder draw</t>
+          <t>Founder draw (income = surplus, NOT a cost)</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Modest early-stage draw</t>
+          <t>Bootstrap: founder takes operating surplus, draws no salary</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Part-time support (from house #2)</t>
+          <t>Part-time help (from house #2)</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Added month 18</t>
+          <t>Cheap local part-time, added month 18</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Second support (late year 3)</t>
+          <t>Second part-timer (house #3)</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Accounting, legal, tools</t>
+          <t>Accounting, tools</t>
         </is>
       </c>
     </row>
@@ -3572,129 +3572,129 @@
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>PEOPLE</t>
+          <t>PEOPLE  (bootstrap — founder draws no salary)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Founder draw</t>
+          <t>Founder draw (none)</t>
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="O5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="R5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="S5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="U5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="V5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="W5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Support (part-time)</t>
+          <t>Part-time help</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
@@ -3749,61 +3749,61 @@
         <v>0</v>
       </c>
       <c r="S6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="T6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="V6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="W6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="X6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="Y6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="Z6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="AA6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="AB6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="AC6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="AD6" s="17" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="AF6" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="AG6" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="AH6" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="AI6" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="AJ6" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="AK6" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7">
@@ -3971,112 +3971,112 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="K10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="N10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="O10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="P10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="S10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="T10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="V10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="W10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="X10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="Y10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="Z10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="AA10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="AB10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="AC10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="AD10" s="17" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>910</v>
+        <v>810</v>
       </c>
       <c r="AF10" s="17" t="n">
-        <v>910</v>
+        <v>810</v>
       </c>
       <c r="AG10" s="17" t="n">
-        <v>910</v>
+        <v>810</v>
       </c>
       <c r="AH10" s="17" t="n">
-        <v>910</v>
+        <v>810</v>
       </c>
       <c r="AI10" s="17" t="n">
-        <v>910</v>
+        <v>810</v>
       </c>
       <c r="AJ10" s="17" t="n">
-        <v>910</v>
+        <v>810</v>
       </c>
       <c r="AK10" s="17" t="n">
-        <v>910</v>
+        <v>810</v>
       </c>
     </row>
     <row r="12">
@@ -4713,7 +4713,7 @@
     <row r="6">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SURPLUS (founder income)</t>
         </is>
       </c>
       <c r="B6" s="26">
@@ -4864,7 +4864,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Cumulative net</t>
+          <t>Cumulative surplus</t>
         </is>
       </c>
       <c r="B7" s="17">
@@ -5090,7 +5090,7 @@
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SURPLUS (founder income)</t>
         </is>
       </c>
       <c r="B14" s="19">
@@ -5120,49 +5120,49 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>•  LEANEST BASE CASE. 3 houses (1 -&gt; 2 -&gt; 3), 15% adoption ceiling, founder-lean costs. Deliberately conservative for a startup breaking a manual market.</t>
+          <t>•  ZIMBABWE BOOTSTRAP. 3 houses (1 -&gt; 2 -&gt; 3), 15% adoption ceiling. No external capital, no founder salary, no hire-ahead. The bottom line is OPERATING SURPLUS = the founder's income.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>•  Investment-stage through all 3 years: Y1 net ~-$19k, Y2 ~-$13k, Y3 ~-$7k. Standalone break-even sits BEYOND month 36.</t>
+          <t>•  Cash-positive from the first live house (month 6). Founder income: ~$6k (Y1) -&gt; ~$18k (Y2) -&gt; ~$32k (Y3); ~$56k over 3 years. Deepest the founder is ever out-of-pocket is ~$2,250 (pre-launch months) -- self-financed, no raise.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>•  The binding constraint is SCALE + FIXED COST, not adoption. Pushing adoption 15% -&gt; 30% improves Y3 monthly net by only ~$200. A mature house contributes ~$15-21k/yr; fixed cost is ~$48-55k/yr.</t>
+          <t>•  No 'runway' or 'break-even month' here -- those are first-world startup artifacts. There is no burn to recover because there is no capital being burnt.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>•  Revenue is retainer-led (Y3: ~$37k retainer of ~$49k total). The recurring spine is reliable; tx-surcharge is small but compounds with adoption.</t>
+          <t>•  Constraint is SCALE + OPERATOR CAPACITY, not adoption. Pushing adoption 15% -&gt; 30% adds only ~$200/mo. Each mature house adds ~$15-30k of surplus; growth is capped by how many an owner + cheap part-time help can run, and is self-funded from surplus.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>•  GMV routed onto Paynow rails: ~$43k (Y1) -&gt; ~$223k (Y2) -&gt; ~$545k (Y3). This is the number that matters most to Paynow and grows fastest.</t>
+          <t>•  Revenue is retainer-led (Y3: ~$37k retainer of ~$49k total). The recurring spine is reliable; tx-surcharge is small but compounds with adoption.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>•  PATH-TO-VIABILITY (NOT base case): with 6 houses by m44, 20% adoption, and transport margin, cumulative net turns positive ~month 36 and reaches ~+$103k by month 60.</t>
+          <t>•  GMV routed onto Paynow rails: ~$43k (Y1) -&gt; ~$223k (Y2) -&gt; ~$545k (Y3). The number that matters most to Paynow and grows fastest.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="29" t="inlineStr">
         <is>
-          <t>•  All figures USD. Not modelled: fundraising (none assumed), corporate tax, working-capital float, transport revenue (upside).</t>
+          <t>•  ZIMBABWE-SPECIFIC RISKS: USD scarcity / collection friction in a cash economy; ZWL/ZiG volatility (price in USD); no capital cushion, so any shock is absorbed by the founder. Corporate tax and transport revenue (upside) not modelled. All figures USD.</t>
         </is>
       </c>
     </row>
